--- a/artfynd/A 53849-2023 artfynd.xlsx
+++ b/artfynd/A 53849-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53849-2023 artfynd.xlsx
+++ b/artfynd/A 53849-2023 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>119959277</v>
       </c>
       <c r="B3" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2023 artfynd.xlsx
+++ b/artfynd/A 53849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>92377221</v>
       </c>
       <c r="B2" t="n">
-        <v>56164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424857.8630463952</v>
+        <v>424858</v>
       </c>
       <c r="R2" t="n">
-        <v>6299528.525953322</v>
+        <v>6299529</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -805,16 +800,11 @@
         <v>119959277</v>
       </c>
       <c r="B3" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -929,6 +919,125 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>92759382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Angelstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424863</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6299656</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Angelstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-04-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vägkant. Lövskog.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53849-2023 artfynd.xlsx
+++ b/artfynd/A 53849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92377221</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119959277</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,8 +1053,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92759382</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>